--- a/generator/affiliate_links.xlsx
+++ b/generator/affiliate_links.xlsx
@@ -569,7 +569,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninja+Air+Fryer+MAX+PRO+62L+AF180UK&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
@@ -609,7 +613,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninja+Foodi+Dual+Zone+76L+AF300UK&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -649,7 +657,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tower+Vortx+4L+T17087&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -689,7 +701,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tefal+Easy+Fry+Dual+XXL+11L+EY942BG0&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -729,7 +745,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+3000+Series+Airfryer+L+NA23100&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
@@ -769,7 +789,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tower+Vortx+4L+T17087&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
@@ -809,7 +833,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=COSORI+47L+Pro+LE&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -849,7 +877,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Salter+EK4548+XL+8L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
@@ -889,7 +921,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Russell+Hobbs+SatisFry+Air+5L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
@@ -929,7 +965,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninja+Air+Fryer+38L+AF100UK&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
@@ -969,7 +1009,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninja+Foodi+Dual+Zone+76L+AF300UK&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1009,7 +1053,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninja+Double+Stack+XL+95L+SL400UK&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1049,7 +1097,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tefal+Easy+Fry+Dual+XXL+11L+EY942BG0&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1089,7 +1141,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tower+Vortx+Eco+Dual+Drawer+85L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1129,7 +1185,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Instant+Vortex+Plus+VersaZone+85L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1169,7 +1229,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninja+Double+Stack+XL+95L+SL400UK&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1209,7 +1273,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tefal+Easy+Fry+Dual+XXL+11L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1249,7 +1317,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninja+Foodi+MAX+15in1+SmartLid+75L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1289,7 +1361,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Salter+Fuzion+Dual+9L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1329,7 +1405,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tower+Vortx+Vizion+14L+Air+Fryer+Oven&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1369,7 +1449,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninja+Air+Fryer+38L+AF100UK&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1409,7 +1493,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=COSORI+Mini+21L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1449,7 +1537,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tower+Vortx+Compact+22L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1489,7 +1581,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+1000+Series+42L+NA12000&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1529,7 +1625,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Instant+Vortex+Slim+57L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1569,7 +1669,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+Series+800i+AC085011&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1609,7 +1713,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Levoit+Core+300S&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1649,7 +1757,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dyson+Purifier+Cool+TP07&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1689,7 +1801,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Levoit+Core+600S&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1729,7 +1845,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Blueair+Blue+Max+3250i&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1769,7 +1889,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+Series+800i+Allergy&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1809,7 +1933,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Levoit+Core+300S+Pet++Pollen&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1849,7 +1977,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Blueair+Blue+Max+3250i+Allergy&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1889,7 +2021,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dyson+Purifier+Cool+TP07+Allergy&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1929,7 +2065,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Vax+Pure+Air+300&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1969,7 +2109,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Blueair+Blue+Max+3250i+Sleep&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2009,7 +2153,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+Series+800i+Sleep&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2049,7 +2197,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Levoit+Core+300S+Sleep&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2089,7 +2241,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Smart+Air+Purifier+4+Compact+Sleep&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2129,7 +2285,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Molekule+Air+Mini+Sleep&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2169,7 +2329,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Levoit+Core+600S+Large&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2209,7 +2373,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+Series+3200+AC322010&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2249,7 +2417,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Blueair+Blue+Max+3450i&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2289,7 +2461,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Smart+Air+Purifier+4+Pro&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2329,7 +2505,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Shark+NeverChange+Air+Purifier+MAX&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2369,7 +2549,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+Series+800i&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2409,7 +2593,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Levoit+Core+300S&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2449,7 +2637,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Levoit+Core+MiniP&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2489,7 +2681,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Smart+Air+Purifier+4+Compact&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2529,7 +2725,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+5in1+HEPA+Purifier&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2569,7 +2769,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Magnifica+S+ECAM22110B&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2609,7 +2813,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Sage+Bambino+Plus&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2649,7 +2857,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Nespresso+Vertuo+Pop+by+Krups&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2689,7 +2901,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Gaggia+Classic+Evo+Pro&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2729,7 +2945,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+2200+LatteGo&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2769,7 +2989,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Magnifica+S+B2C&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2809,7 +3033,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Philips+3200+LatteGo&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2849,7 +3077,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Dinamica+Plus&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2889,7 +3121,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Jura+E6+Platin&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2929,7 +3165,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Melitta+Caffeo+Solo&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2969,7 +3209,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Nespresso+Vertuo+Pop+Budget&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
@@ -3009,7 +3253,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Stilosa+EC260&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
@@ -3049,7 +3297,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr"/>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Melitta+Look+V+Timer+Filter&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
@@ -3089,7 +3341,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=AeroPress++JX+Manual+Grinder+bundle&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
@@ -3129,7 +3385,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tassimo+by+Bosch+Style&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
@@ -3169,7 +3429,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Nespresso+Essenza+Mini+Original&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
@@ -3209,7 +3473,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Nespresso+Vertuo+Next&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
@@ -3249,7 +3517,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=LOR+Barista+Sublime&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
@@ -3289,7 +3561,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Nescaf+Dolce+Gusto+Genio+S+Plus&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
@@ -3329,7 +3605,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Nespresso+Creatista+Plus+by+Sage&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3369,7 +3649,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Sage+Bambino+Plus+Beginner&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3409,7 +3693,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Dedica+Style+EC685&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3449,7 +3737,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Gaggia+Classic+Evo+Pro+Beginner&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
@@ -3489,7 +3781,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Stilosa+Beginner&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
@@ -3529,7 +3825,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Sage+Barista+Express&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
@@ -3569,7 +3869,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=MeacoDry+Arete+One+12L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
@@ -3609,7 +3913,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Meaco+Low+Energy+20L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
@@ -3649,7 +3957,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+12L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
@@ -3689,7 +4001,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=EcoAir+DD1+Simple+MK3+Desiccant&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
@@ -3729,7 +4045,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=ElectriQ+CD12PROLE&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
@@ -3769,7 +4089,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=MeacoDry+Arete+One+10L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
@@ -3809,7 +4133,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+500ml+Mini&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3849,7 +4177,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=EcoAir+DD1+Simple+MK3&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3889,7 +4221,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Russell+Hobbs+RHDH1101&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
@@ -3929,7 +4265,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Duux+Bora+Smart+20L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
@@ -3969,7 +4309,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Meaco+Low+Energy+25L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
@@ -4009,7 +4353,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Meaco+Low+Energy+20L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4049,7 +4397,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=ElectriQ+CD25PROLEV2&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
@@ -4089,7 +4441,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+20L+Premium&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4129,7 +4485,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Inventor+Eva+Ion+Pro+20L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4169,7 +4529,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Meaco+Low+Energy+20L+Laundry&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
@@ -4209,7 +4573,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=MeacoDry+Arete+One+12L+Laundry&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
@@ -4249,7 +4617,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=EcoAir+DD1+Simple+MK3+Laundry&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
@@ -4289,7 +4661,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+20L+Premium+Laundry&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
@@ -4329,7 +4705,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Vax+Power+Extract+18L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
@@ -4369,7 +4749,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=MeacoDry+Arete+One+20L&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
@@ -4409,7 +4793,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=ElectriQ+CD20PROLEV2+UV&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
@@ -4449,7 +4837,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Meaco+Low+Energy+25L+Damp+Rescue&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
@@ -4489,7 +4881,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+12L+Compressor+Starter&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
@@ -4529,7 +4925,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ionmax+ION632+Desiccant&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
@@ -4569,7 +4969,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Decathlon+Btwin+LD+920+E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
@@ -4609,7 +5013,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Engwe+P20&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
@@ -4649,7 +5057,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Cube+Touring+Hybrid+One+500&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
@@ -4689,7 +5101,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr"/>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Fiido+D11&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
@@ -4729,7 +5145,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Trek+FX+2&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
@@ -4769,7 +5189,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Engwe+P20&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
@@ -4809,7 +5233,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Eleglide+M1+Plus&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
@@ -4849,7 +5277,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Fiido+D11&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
@@ -4889,7 +5321,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Decathlon+Btwin+EFold+500&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
@@ -4929,7 +5365,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=ADO+Air+20&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
@@ -4969,7 +5409,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I112" s="4" t="inlineStr"/>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=ADO+Air+20&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
@@ -5009,7 +5453,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Brompton+Electric+C+Line&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
@@ -5049,7 +5497,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Fiido+X&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
@@ -5089,7 +5541,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Decathlon+Btwin+EFold+900&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
@@ -5129,7 +5585,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I116" s="4" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Engwe+C20+Pro&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
@@ -5169,7 +5629,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Decathlon+Rockrider+EEXPL+520&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
@@ -5209,7 +5673,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Cube+Reaction+Hybrid+Performance+625&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
@@ -5249,7 +5717,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Giant+Talon+E+3&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
@@ -5289,7 +5761,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr"/>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Engwe+Engine+Pro+20&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
@@ -5329,7 +5805,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I121" s="4" t="inlineStr"/>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Specialized+Turbo+Tero+30&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
@@ -5369,7 +5849,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I122" s="4" t="inlineStr"/>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Decathlon+Btwin+LD+920+E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
@@ -5409,7 +5893,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I123" s="4" t="inlineStr"/>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Cube+Touring+Hybrid+One+500&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
@@ -5449,7 +5937,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I124" s="4" t="inlineStr"/>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Gazelle+Paris+C7+HMB&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
@@ -5489,7 +5981,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I125" s="4" t="inlineStr"/>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Eleglide+T1+StepThru&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
@@ -5529,7 +6025,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Tenways+CGO600+Pro&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
@@ -5569,7 +6069,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Dragon+4+25kW+Oil+Radiator+TRD41025T&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J127" s="5" t="inlineStr"/>
     </row>
     <row r="128">
@@ -5609,7 +6113,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I128" s="4" t="inlineStr"/>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dyson+HotCool+Jet+Focus+AM09&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
@@ -5649,7 +6157,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+2kW+Ceramic+Fan+Heater&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
@@ -5689,7 +6201,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I130" s="4" t="inlineStr"/>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Stiebel+Eltron+CK+20+S+Wall+Heater&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J130" s="5" t="inlineStr"/>
     </row>
     <row r="131">
@@ -5729,7 +6245,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I131" s="4" t="inlineStr"/>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Devola+2kW+Smart+Glass+Panel+Heater&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
@@ -5769,7 +6289,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I132" s="4" t="inlineStr"/>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Vonhaus+550W+Glass+Panel+Heater&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
@@ -5809,7 +6333,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I133" s="4" t="inlineStr"/>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+1200W+Halogen+Heater&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
@@ -5849,7 +6377,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I134" s="4" t="inlineStr"/>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Duronic+HV052+UnderDesk+Heater&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
@@ -5889,7 +6421,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I135" s="4" t="inlineStr"/>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Radia+S+15kW+Oil+Radiator+TRRS0715&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
@@ -5929,7 +6465,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr"/>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Devola+15kW+Smart+WiFi+Panel&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
@@ -5969,7 +6509,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr"/>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Dragon+4+25kW+TRD41025T&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
@@ -6009,7 +6553,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I138" s="4" t="inlineStr"/>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+25kW+Digital+Oil+Radiator&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
@@ -6049,7 +6597,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr"/>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dimplex+2kW+ECR20Tie+Cadiz&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
@@ -6089,7 +6641,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I140" s="4" t="inlineStr"/>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=VonHaus+15kW+7Fin+Oil+Radiator&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J140" s="5" t="inlineStr"/>
     </row>
     <row r="141">
@@ -6129,7 +6685,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I141" s="4" t="inlineStr"/>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=DeLonghi+Radia+S+2kW+with+Timer+TRRS0920T&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
@@ -6169,7 +6729,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I142" s="4" t="inlineStr"/>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Devola+2kW+Smart+Glass+Panel&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
@@ -6209,7 +6773,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I143" s="4" t="inlineStr"/>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Mylek+15kW+Smart+Panel&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
@@ -6249,7 +6817,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I144" s="4" t="inlineStr"/>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dimplex+DTD4W20+Panel+Heater&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
@@ -6289,7 +6861,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I145" s="4" t="inlineStr"/>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Princess+15kW+Smart+Glass+Panel&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
@@ -6329,7 +6905,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I146" s="4" t="inlineStr"/>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Warmlite+1kW+Slim+Panel&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J146" s="5" t="inlineStr"/>
     </row>
     <row r="147">
@@ -6369,7 +6949,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Stiebel+Eltron+CK+20+S&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J147" s="5" t="inlineStr"/>
     </row>
     <row r="148">
@@ -6409,7 +6993,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I148" s="4" t="inlineStr"/>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pro+Breeze+2kW+Mini+Ceramic&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J148" s="5" t="inlineStr"/>
     </row>
     <row r="149">
@@ -6449,7 +7037,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I149" s="4" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dimplex+2kW+Downflow+Bathroom+Heater+FX20VE&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J149" s="5" t="inlineStr"/>
     </row>
     <row r="150">
@@ -6489,7 +7081,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I150" s="4" t="inlineStr"/>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Devola+550W+Towel+Rail++Timer&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
@@ -6529,7 +7125,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I151" s="4" t="inlineStr"/>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=VonHaus+18kW+Wall+Ceramic+Heater&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
@@ -6569,7 +7169,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I152" s="4" t="inlineStr"/>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Electric+Scooter+4+Pro+2nd+Gen&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J152" s="5" t="inlineStr"/>
     </row>
     <row r="153">
@@ -6609,7 +7213,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr"/>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Ninebot+MAX+G2+E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
@@ -6649,7 +7257,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr"/>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Aovo+Pro+AP07&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J154" s="5" t="inlineStr"/>
     </row>
     <row r="155">
@@ -6689,7 +7301,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pure+Advance+Flex&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J155" s="5" t="inlineStr"/>
     </row>
     <row r="156">
@@ -6729,7 +7345,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I156" s="4" t="inlineStr"/>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ninebot+KickScooter+F2+E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
@@ -6769,7 +7389,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I157" s="4" t="inlineStr"/>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Electric+Scooter+4+Lite+2nd+Gen&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J157" s="5" t="inlineStr"/>
     </row>
     <row r="158">
@@ -6809,7 +7433,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I158" s="4" t="inlineStr"/>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Aovo+Pro+M365+Upgraded&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J158" s="5" t="inlineStr"/>
     </row>
     <row r="159">
@@ -6849,7 +7477,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I159" s="4" t="inlineStr"/>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Ninebot+E2+Pro+E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
@@ -6889,7 +7521,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I160" s="4" t="inlineStr"/>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=iScooter+i9+Max&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J160" s="5" t="inlineStr"/>
     </row>
     <row r="161">
@@ -6929,7 +7565,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Electric+Scooter+4+Standard&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J161" s="5" t="inlineStr"/>
     </row>
     <row r="162">
@@ -6969,7 +7609,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I162" s="4" t="inlineStr"/>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Ninebot+MAX+G3+E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J162" s="5" t="inlineStr"/>
     </row>
     <row r="163">
@@ -7009,7 +7653,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I163" s="4" t="inlineStr"/>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pure+Advance+&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J163" s="5" t="inlineStr"/>
     </row>
     <row r="164">
@@ -7049,7 +7697,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I164" s="4" t="inlineStr"/>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Electric+Scooter+5+Max&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J164" s="5" t="inlineStr"/>
     </row>
     <row r="165">
@@ -7089,7 +7741,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I165" s="4" t="inlineStr"/>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=NIU+KQi3+Max&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J165" s="5" t="inlineStr"/>
     </row>
     <row r="166">
@@ -7129,7 +7785,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr"/>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=VMAX+VX2+Pro+GT&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J166" s="5" t="inlineStr"/>
     </row>
     <row r="167">
@@ -7169,7 +7829,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I167" s="4" t="inlineStr"/>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Mi+Electric+Scooter+3+Lite&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
@@ -7209,7 +7873,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I168" s="4" t="inlineStr"/>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Ninebot+Air+T15E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
@@ -7249,7 +7917,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I169" s="4" t="inlineStr"/>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Pure+Air4&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J169" s="5" t="inlineStr"/>
     </row>
     <row r="170">
@@ -7289,7 +7961,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I170" s="4" t="inlineStr"/>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=iScooter+i8&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J170" s="5" t="inlineStr"/>
     </row>
     <row r="171">
@@ -7329,7 +8005,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I171" s="4" t="inlineStr"/>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=ducati+ProI+Evo+Safe+Ride&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J171" s="5" t="inlineStr"/>
     </row>
     <row r="172">
@@ -7369,7 +8049,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I172" s="4" t="inlineStr"/>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Ninebot+MAX+G2+E+120+kg&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J172" s="5" t="inlineStr"/>
     </row>
     <row r="173">
@@ -7409,7 +8093,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I173" s="4" t="inlineStr"/>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=VMAX+VX2+Pro+ST&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J173" s="5" t="inlineStr"/>
     </row>
     <row r="174">
@@ -7449,7 +8137,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I174" s="4" t="inlineStr"/>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Electric+Scooter+5+Max+118+kg&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J174" s="5" t="inlineStr"/>
     </row>
     <row r="175">
@@ -7489,7 +8181,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I175" s="4" t="inlineStr"/>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=NIU+KQi+300X&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J175" s="5" t="inlineStr"/>
     </row>
     <row r="176">
@@ -7529,7 +8225,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I176" s="4" t="inlineStr"/>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=iScooter+iX4&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J176" s="5" t="inlineStr"/>
     </row>
     <row r="177">
@@ -7569,7 +8269,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr"/>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=SIHOO+Doro+C300&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J177" s="5" t="inlineStr"/>
     </row>
     <row r="178">
@@ -7609,7 +8313,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr"/>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Herman+Miller+Aeron+Remastered&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J178" s="5" t="inlineStr"/>
     </row>
     <row r="179">
@@ -7649,7 +8357,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr"/>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Steelcase+Series+1&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J179" s="5" t="inlineStr"/>
     </row>
     <row r="180">
@@ -7689,7 +8401,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr"/>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Flexispot+BS11+Pro+C7&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J180" s="5" t="inlineStr"/>
     </row>
     <row r="181">
@@ -7729,7 +8445,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr"/>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=IKEA+MARKUS&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J181" s="5" t="inlineStr"/>
     </row>
     <row r="182">
@@ -7769,7 +8489,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr"/>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=IKEA+MARKUS+Budget&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J182" s="5" t="inlineStr"/>
     </row>
     <row r="183">
@@ -7809,7 +8533,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I183" s="4" t="inlineStr"/>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=SIHOO+M18&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J183" s="5" t="inlineStr"/>
     </row>
     <row r="184">
@@ -7849,7 +8577,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I184" s="4" t="inlineStr"/>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Songmics+OBN37BK&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J184" s="5" t="inlineStr"/>
     </row>
     <row r="185">
@@ -7889,7 +8621,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I185" s="4" t="inlineStr"/>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Flexispot+OC3&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J185" s="5" t="inlineStr"/>
     </row>
     <row r="186">
@@ -7929,7 +8665,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=HBADA+E1+Ergonomic&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J186" s="5" t="inlineStr"/>
     </row>
     <row r="187">
@@ -7969,7 +8709,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I187" s="4" t="inlineStr"/>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Flexispot+E7+Pro&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J187" s="5" t="inlineStr"/>
     </row>
     <row r="188">
@@ -8009,7 +8753,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I188" s="4" t="inlineStr"/>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=IKEA+TROTTEN+Electric+manual+crank&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J188" s="5" t="inlineStr"/>
     </row>
     <row r="189">
@@ -8049,7 +8797,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I189" s="4" t="inlineStr"/>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Flexispot+E7&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J189" s="5" t="inlineStr"/>
     </row>
     <row r="190">
@@ -8089,7 +8841,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I190" s="4" t="inlineStr"/>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Songmics+LSD012+Electric&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J190" s="5" t="inlineStr"/>
     </row>
     <row r="191">
@@ -8129,7 +8885,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I191" s="4" t="inlineStr"/>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Secretlab+MAGNUS+Pro++tabletop&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J191" s="5" t="inlineStr"/>
     </row>
     <row r="192">
@@ -8169,7 +8929,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr"/>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Flexispot+E7++10060+top&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J192" s="5" t="inlineStr"/>
     </row>
     <row r="193">
@@ -8209,7 +8973,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr"/>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=IKEA+MICKE+10550&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J193" s="5" t="inlineStr"/>
     </row>
     <row r="194">
@@ -8249,7 +9017,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I194" s="4" t="inlineStr"/>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Habitat+Compton+Folding+Desk&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J194" s="5" t="inlineStr"/>
     </row>
     <row r="195">
@@ -8289,7 +9061,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I195" s="4" t="inlineStr"/>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=VASAGLE+LShaped+Corner+Desk+130&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J195" s="5" t="inlineStr"/>
     </row>
     <row r="196">
@@ -8329,7 +9105,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I196" s="4" t="inlineStr"/>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=String+Furniture+Works+Wall+Desk+78&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J196" s="5" t="inlineStr"/>
     </row>
     <row r="197">
@@ -8369,7 +9149,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I197" s="4" t="inlineStr"/>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Flexispot+M7B+Converter+35&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J197" s="5" t="inlineStr"/>
     </row>
     <row r="198">
@@ -8409,7 +9193,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I198" s="4" t="inlineStr"/>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ergotron+LX+Monitor+Arm&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J198" s="5" t="inlineStr"/>
     </row>
     <row r="199">
@@ -8449,7 +9237,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I199" s="4" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=HUANUO+Dual+Monitor+Arm&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J199" s="5" t="inlineStr"/>
     </row>
     <row r="200">
@@ -8489,7 +9281,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I200" s="4" t="inlineStr"/>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Kensington+SoleMate+Pro+Footrest&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J200" s="5" t="inlineStr"/>
     </row>
     <row r="201">
@@ -8529,7 +9325,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I201" s="4" t="inlineStr"/>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Topo+AntiFatigue+Mat+by+Ergodriven&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J201" s="5" t="inlineStr"/>
     </row>
     <row r="202">
@@ -8569,7 +9369,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I202" s="4" t="inlineStr"/>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Navimow+i105E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J202" s="5" t="inlineStr"/>
     </row>
     <row r="203">
@@ -8609,7 +9413,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I203" s="4" t="inlineStr"/>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Husqvarna+Automower+305&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J203" s="5" t="inlineStr"/>
     </row>
     <row r="204">
@@ -8649,7 +9457,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I204" s="4" t="inlineStr"/>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Worx+Landroid+Vision+M600&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J204" s="5" t="inlineStr"/>
     </row>
     <row r="205">
@@ -8689,7 +9501,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I205" s="4" t="inlineStr"/>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Gardena+Sileno+City+250&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J205" s="5" t="inlineStr"/>
     </row>
     <row r="206">
@@ -8729,7 +9545,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I206" s="4" t="inlineStr"/>
+      <c r="I206" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Navimow+i110E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J206" s="5" t="inlineStr"/>
     </row>
     <row r="207">
@@ -8769,7 +9589,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I207" s="4" t="inlineStr"/>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Gardena+Sileno+City+250+Small&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J207" s="5" t="inlineStr"/>
     </row>
     <row r="208">
@@ -8809,7 +9633,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I208" s="4" t="inlineStr"/>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Navimow+i105E+Small&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J208" s="5" t="inlineStr"/>
     </row>
     <row r="209">
@@ -8849,7 +9677,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I209" s="4" t="inlineStr"/>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Worx+Landroid+S300&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J209" s="5" t="inlineStr"/>
     </row>
     <row r="210">
@@ -8889,7 +9721,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I210" s="4" t="inlineStr"/>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Flymo+EasiLife+GO+250&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J210" s="5" t="inlineStr"/>
     </row>
     <row r="211">
@@ -8929,7 +9765,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I211" s="4" t="inlineStr"/>
+      <c r="I211" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Bosch+Indego+S+350&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J211" s="5" t="inlineStr"/>
     </row>
     <row r="212">
@@ -8969,7 +9809,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I212" s="4" t="inlineStr"/>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Navimow+i110E+Large&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J212" s="5" t="inlineStr"/>
     </row>
     <row r="213">
@@ -9009,7 +9853,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I213" s="4" t="inlineStr"/>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Husqvarna+Automower+430X+NERA&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J213" s="5" t="inlineStr"/>
     </row>
     <row r="214">
@@ -9049,7 +9897,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I214" s="4" t="inlineStr"/>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Navimow+H1500E&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J214" s="5" t="inlineStr"/>
     </row>
     <row r="215">
@@ -9089,7 +9941,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I215" s="4" t="inlineStr"/>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Worx+Landroid+L2000&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J215" s="5" t="inlineStr"/>
     </row>
     <row r="216">
@@ -9129,7 +9985,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I216" s="4" t="inlineStr"/>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ecovacs+Goat+G12000&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J216" s="5" t="inlineStr"/>
     </row>
     <row r="217">
@@ -9169,7 +10029,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I217" s="4" t="inlineStr"/>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Segway+Navimow+i105E+WireFree&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J217" s="5" t="inlineStr"/>
     </row>
     <row r="218">
@@ -9209,7 +10073,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I218" s="4" t="inlineStr"/>
+      <c r="I218" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Worx+Landroid+Vision+M600+WireFree&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J218" s="5" t="inlineStr"/>
     </row>
     <row r="219">
@@ -9249,7 +10117,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I219" s="4" t="inlineStr"/>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Husqvarna+Automower+320+NERA++EPOS&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J219" s="5" t="inlineStr"/>
     </row>
     <row r="220">
@@ -9289,7 +10161,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I220" s="4" t="inlineStr"/>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Ecovacs+Goat+G1800&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J220" s="5" t="inlineStr"/>
     </row>
     <row r="221">
@@ -9329,7 +10205,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I221" s="4" t="inlineStr"/>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Mammotion+Luba+2+AWD+1000&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J221" s="5" t="inlineStr"/>
     </row>
     <row r="222">
@@ -9369,7 +10249,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I222" s="4" t="inlineStr"/>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Gardena+Sileno+City+250+Budget&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J222" s="5" t="inlineStr"/>
     </row>
     <row r="223">
@@ -9409,7 +10293,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I223" s="4" t="inlineStr"/>
+      <c r="I223" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Flymo+EasiLife+GO+500&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J223" s="5" t="inlineStr"/>
     </row>
     <row r="224">
@@ -9449,7 +10337,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I224" s="4" t="inlineStr"/>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Worx+Landroid+S300+Budget&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J224" s="5" t="inlineStr"/>
     </row>
     <row r="225">
@@ -9489,7 +10381,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I225" s="4" t="inlineStr"/>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Yard+Force+Compact+300RBS&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J225" s="5" t="inlineStr"/>
     </row>
     <row r="226">
@@ -9529,7 +10425,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I226" s="4" t="inlineStr"/>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Einhell+FREELEXO+400m+BT&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J226" s="5" t="inlineStr"/>
     </row>
     <row r="227">
@@ -9569,7 +10469,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I227" s="4" t="inlineStr"/>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Roborock+Q8+Max&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J227" s="5" t="inlineStr"/>
     </row>
     <row r="228">
@@ -9609,7 +10513,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I228" s="4" t="inlineStr"/>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Roborock+S8+MaxV+Ultra&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J228" s="5" t="inlineStr"/>
     </row>
     <row r="229">
@@ -9649,7 +10557,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I229" s="4" t="inlineStr"/>
+      <c r="I229" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Eufy+RoboVac+11S+MAX&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J229" s="5" t="inlineStr"/>
     </row>
     <row r="230">
@@ -9689,7 +10601,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I230" s="4" t="inlineStr"/>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dreame+L10s+Ultra+Gen+2&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J230" s="5" t="inlineStr"/>
     </row>
     <row r="231">
@@ -9729,7 +10645,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I231" s="4" t="inlineStr"/>
+      <c r="I231" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=iRobot+Roomba+Combo+j7&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J231" s="5" t="inlineStr"/>
     </row>
     <row r="232">
@@ -9769,7 +10689,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I232" s="4" t="inlineStr"/>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Roborock+Q7+L5&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J232" s="5" t="inlineStr"/>
     </row>
     <row r="233">
@@ -9809,7 +10733,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I233" s="4" t="inlineStr"/>
+      <c r="I233" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Eufy+RoboVac+11S+MAX+Budget&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J233" s="5" t="inlineStr"/>
     </row>
     <row r="234">
@@ -9849,7 +10777,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I234" s="4" t="inlineStr"/>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dreame+D10+Plus+Gen+2&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J234" s="5" t="inlineStr"/>
     </row>
     <row r="235">
@@ -9889,7 +10821,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I235" s="4" t="inlineStr"/>
+      <c r="I235" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+Robot+Vacuum+S20&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J235" s="5" t="inlineStr"/>
     </row>
     <row r="236">
@@ -9929,7 +10865,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I236" s="4" t="inlineStr"/>
+      <c r="I236" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Lefant+M310&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J236" s="5" t="inlineStr"/>
     </row>
     <row r="237">
@@ -9969,7 +10909,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I237" s="4" t="inlineStr"/>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=iRobot+Roomba+Combo+j7+Pets&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J237" s="5" t="inlineStr"/>
     </row>
     <row r="238">
@@ -10009,7 +10953,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I238" s="4" t="inlineStr"/>
+      <c r="I238" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Roborock+Q8+Max+Pets&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J238" s="5" t="inlineStr"/>
     </row>
     <row r="239">
@@ -10049,7 +10997,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I239" s="4" t="inlineStr"/>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dreame+L10s+Ultra+Gen+2+Pets&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J239" s="5" t="inlineStr"/>
     </row>
     <row r="240">
@@ -10089,7 +11041,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I240" s="4" t="inlineStr"/>
+      <c r="I240" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Eufy+X10+Pro+Omni+Pets&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J240" s="5" t="inlineStr"/>
     </row>
     <row r="241">
@@ -10129,7 +11085,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I241" s="4" t="inlineStr"/>
+      <c r="I241" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Shark+Matrix+Plus+2in1+Pets&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J241" s="5" t="inlineStr"/>
     </row>
     <row r="242">
@@ -10169,7 +11129,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I242" s="4" t="inlineStr"/>
+      <c r="I242" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Roborock+S8+MaxV+Ultra+Mop&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J242" s="5" t="inlineStr"/>
     </row>
     <row r="243">
@@ -10209,7 +11173,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I243" s="4" t="inlineStr"/>
+      <c r="I243" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dreame+L10s+Ultra+Gen+2+Mop&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J243" s="5" t="inlineStr"/>
     </row>
     <row r="244">
@@ -10249,7 +11217,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I244" s="4" t="inlineStr"/>
+      <c r="I244" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Eufy+X10+Pro+Omni+Mop&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J244" s="5" t="inlineStr"/>
     </row>
     <row r="245">
@@ -10289,7 +11261,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I245" s="4" t="inlineStr"/>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Roborock+Q+Revo&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J245" s="5" t="inlineStr"/>
     </row>
     <row r="246">
@@ -10329,7 +11305,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I246" s="4" t="inlineStr"/>
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Xiaomi+X20&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J246" s="5" t="inlineStr"/>
     </row>
     <row r="247">
@@ -10369,7 +11349,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I247" s="4" t="inlineStr"/>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Roborock+S8+MaxV+Ultra+Premium&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J247" s="5" t="inlineStr"/>
     </row>
     <row r="248">
@@ -10409,7 +11393,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I248" s="4" t="inlineStr"/>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Dreame+X40+Ultra&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J248" s="5" t="inlineStr"/>
     </row>
     <row r="249">
@@ -10449,7 +11437,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I249" s="4" t="inlineStr"/>
+      <c r="I249" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=iRobot+Roomba+j9+Combo&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J249" s="5" t="inlineStr"/>
     </row>
     <row r="250">
@@ -10489,7 +11481,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I250" s="4" t="inlineStr"/>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Eufy+Omni+S1+Pro&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J250" s="5" t="inlineStr"/>
     </row>
     <row r="251">
@@ -10529,7 +11525,11 @@
           <t>abrir produto →</t>
         </is>
       </c>
-      <c r="I251" s="4" t="inlineStr"/>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ie/s?k=Roborock+Q+Revo+Premium+Entry&amp;tag=elevaonline-21</t>
+        </is>
+      </c>
       <c r="J251" s="5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/generator/affiliate_links.xlsx
+++ b/generator/affiliate_links.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="694">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -859,7 +859,61 @@
     <t xml:space="preserve">best-electric-bikes-ireland</t>
   </si>
   <si>
-    <t xml:space="preserve">VARUN 26" Electric Bike (250W, Removable Battery)</t>
+    <t xml:space="preserve">ENGWE Folding E-Bike (48V 15Ah, Torque Sensor, 130 km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGWE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0FMRCLHYN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0FMRCLHYN?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGWE Folding E-Bike (48V 13Ah, up to 120 km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0FJKTFCCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0FJKTFCCT?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fafrees F20 X-MAX (48V 30Ah / 1440Wh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fafrees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0CLB7ZZCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0CLB7ZZCS?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGWE 20"×4.0 Fat Step-Through E-Bike (7-Speed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0DWFJCJZ3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0DWFJCJZ3?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARUN 24"/26" Electric Bike (250W, Removable Battery)</t>
   </si>
   <si>
     <t xml:space="preserve">VARUN</t>
@@ -871,19 +925,85 @@
     <t xml:space="preserve">https://www.amazon.ie/dp/B0C7VPVX5B?tag=elevaonline-21</t>
   </si>
   <si>
-    <t xml:space="preserve">ebk-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARUN 27.5" Electric Mountain Bike (App, 624Wh)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B0BVR6V53X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.ie/dp/B0BVR6V53X?tag=elevaonline-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-003</t>
+    <t xml:space="preserve">ebk-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best-electric-bikes-under-1000-ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fafrees 26" Hailong-One E-Bike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0DW8LNFT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0DW8LNFT7?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARUN 27.5" Electric Mountain Bike (624Wh, App)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0BVR81S6P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0BVR81S6P?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARUN 26"×4.0 Fat Tyre E-Bike (48V 18Ah)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0CY2672XJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0CY2672XJ?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fafrees F20 Folding Fat E-Bike (20")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B09QGCQ6GH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B09QGCQ6GH?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best-folding-electric-bikes-ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARUN 20"×4.0 Fat Folding E-Bike (48V 13Ah)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0CZLBRLH7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0CZLBRLH7?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-015</t>
   </si>
   <si>
     <t xml:space="preserve">VARUN 14" Folding Electric Bike</t>
@@ -895,7 +1015,25 @@
     <t xml:space="preserve">https://www.amazon.ie/dp/B0FVRT9WBW?tag=elevaonline-21</t>
   </si>
   <si>
-    <t xml:space="preserve">ebk-004</t>
+    <t xml:space="preserve">ebk-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best-electric-mountain-bikes-ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fafrees F26 Lasting E-MTB (36V 20.3Ah)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0D5CZC4YK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0D5CZC4YK?tag=elevaonline-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebk-018</t>
   </si>
   <si>
     <t xml:space="preserve">Lohang Dual-Motor Electric Bike (52V 24Ah)</t>
@@ -910,81 +1048,18 @@
     <t xml:space="preserve">https://www.amazon.ie/dp/B0F18KS9SK?tag=elevaonline-21</t>
   </si>
   <si>
-    <t xml:space="preserve">ebk-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENGWE Folding Electric Bike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENGWE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B0DBLSYLZS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.ie/dp/B0DBLSYLZS?tag=elevaonline-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best-electric-bikes-under-1000-ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best-folding-electric-bikes-ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best-electric-mountain-bikes-ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARUN 26" Fat Tyre Electric Mountain Bike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B0CN2SFH4N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.ie/dp/B0CN2SFH4N?tag=elevaonline-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebk-018</t>
-  </si>
-  <si>
     <t xml:space="preserve">ebk-019</t>
   </si>
   <si>
+    <t xml:space="preserve">ENGWE E-Bike with APP (48V 13.5Ah, 135 km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0F2TFV2HD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0F2TFV2HD?tag=elevaonline-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">ebk-020</t>
   </si>
   <si>
@@ -1004,6 +1079,15 @@
   </si>
   <si>
     <t xml:space="preserve">ebk-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fafrees F20 Mate Electric Tricycle (873 Wh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0F4X9D75Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ie/dp/B0F4X9D75Z?tag=elevaonline-21</t>
   </si>
   <si>
     <t xml:space="preserve">eht-001</t>
@@ -2465,14 +2549,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6536,7 +6620,7 @@
         <v>279</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>599</v>
+        <v>1699</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>280</v>
@@ -6553,7 +6637,7 @@
       </c>
       <c r="M102" s="6" t="n">
         <f aca="false">G102*L102</f>
-        <v>59.9</v>
+        <v>169.9</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6576,7 +6660,7 @@
         <v>279</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>799</v>
+        <v>1049</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>284</v>
@@ -6593,7 +6677,7 @@
       </c>
       <c r="M103" s="6" t="n">
         <f aca="false">G103*L103</f>
-        <v>79.9</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6613,19 +6697,19 @@
         <v>287</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>459</v>
+        <v>1999</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K104" s="2"/>
       <c r="L104" s="5" t="n">
@@ -6633,12 +6717,12 @@
       </c>
       <c r="M104" s="6" t="n">
         <f aca="false">G104*L104</f>
-        <v>45.9</v>
+        <v>199.9</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>276</v>
@@ -6650,13 +6734,13 @@
         <v>4</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>1099</v>
+        <v>1149</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>293</v>
@@ -6673,7 +6757,7 @@
       </c>
       <c r="M105" s="6" t="n">
         <f aca="false">G105*L105</f>
-        <v>109.9</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6696,7 +6780,7 @@
         <v>297</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>699</v>
+        <v>549</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>298</v>
@@ -6713,7 +6797,7 @@
       </c>
       <c r="M106" s="6" t="n">
         <f aca="false">G106*L106</f>
-        <v>69.9</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6730,22 +6814,22 @@
         <v>1</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="5" t="n">
@@ -6753,7 +6837,7 @@
       </c>
       <c r="M107" s="6" t="n">
         <f aca="false">G107*L107</f>
-        <v>59.9</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6770,22 +6854,22 @@
         <v>2</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>459</v>
+        <v>699</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="K108" s="2"/>
       <c r="L108" s="5" t="n">
@@ -6793,12 +6877,12 @@
       </c>
       <c r="M108" s="6" t="n">
         <f aca="false">G108*L108</f>
-        <v>45.9</v>
+        <v>69.9</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>276</v>
@@ -6810,22 +6894,22 @@
         <v>3</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>297</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>699</v>
+        <v>749</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="5" t="n">
@@ -6833,12 +6917,12 @@
       </c>
       <c r="M109" s="6" t="n">
         <f aca="false">G109*L109</f>
-        <v>69.9</v>
+        <v>74.9</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>276</v>
@@ -6850,22 +6934,22 @@
         <v>4</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>799</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="5" t="n">
@@ -6878,7 +6962,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>276</v>
@@ -6890,22 +6974,22 @@
         <v>5</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1099</v>
+        <v>899</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="K111" s="2"/>
       <c r="L111" s="5" t="n">
@@ -6913,39 +6997,39 @@
       </c>
       <c r="M111" s="6" t="n">
         <f aca="false">G111*L111</f>
-        <v>109.9</v>
+        <v>89.9</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>279</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>459</v>
+        <v>1699</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="5" t="n">
@@ -6953,39 +7037,39 @@
       </c>
       <c r="M112" s="6" t="n">
         <f aca="false">G112*L112</f>
-        <v>45.9</v>
+        <v>169.9</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>699</v>
+        <v>1049</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="K113" s="2"/>
       <c r="L113" s="5" t="n">
@@ -6993,39 +7077,39 @@
       </c>
       <c r="M113" s="6" t="n">
         <f aca="false">G113*L113</f>
-        <v>69.9</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>599</v>
+        <v>899</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="5" t="n">
@@ -7033,39 +7117,39 @@
       </c>
       <c r="M114" s="6" t="n">
         <f aca="false">G114*L114</f>
-        <v>59.9</v>
+        <v>89.9</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>283</v>
+        <v>323</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>799</v>
+        <v>849</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>284</v>
+        <v>324</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="5" t="n">
@@ -7073,39 +7157,39 @@
       </c>
       <c r="M115" s="6" t="n">
         <f aca="false">G115*L115</f>
-        <v>79.9</v>
+        <v>84.9</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1099</v>
+        <v>459</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="5" t="n">
@@ -7113,39 +7197,39 @@
       </c>
       <c r="M116" s="6" t="n">
         <f aca="false">G116*L116</f>
-        <v>109.9</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>799</v>
+        <v>749</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="K117" s="2"/>
       <c r="L117" s="5" t="n">
@@ -7153,39 +7237,39 @@
       </c>
       <c r="M117" s="6" t="n">
         <f aca="false">G117*L117</f>
-        <v>79.9</v>
+        <v>74.9</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>1149</v>
+        <v>899</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="K118" s="2"/>
       <c r="L118" s="5" t="n">
@@ -7193,39 +7277,39 @@
       </c>
       <c r="M118" s="6" t="n">
         <f aca="false">G118*L118</f>
-        <v>114.9</v>
+        <v>89.9</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>1099</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="5" t="n">
@@ -7238,34 +7322,34 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>279</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>599</v>
+        <v>1399</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>280</v>
+        <v>343</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="5" t="n">
@@ -7273,39 +7357,39 @@
       </c>
       <c r="M120" s="6" t="n">
         <f aca="false">G120*L120</f>
-        <v>59.9</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>297</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>699</v>
+        <v>799</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="5" t="n">
@@ -7313,39 +7397,39 @@
       </c>
       <c r="M121" s="6" t="n">
         <f aca="false">G121*L121</f>
-        <v>69.9</v>
+        <v>79.9</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>279</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>599</v>
+        <v>1149</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="5" t="n">
@@ -7353,39 +7437,39 @@
       </c>
       <c r="M122" s="6" t="n">
         <f aca="false">G122*L122</f>
-        <v>59.9</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>279</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>459</v>
+        <v>1049</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="5" t="n">
@@ -7393,39 +7477,39 @@
       </c>
       <c r="M123" s="6" t="n">
         <f aca="false">G123*L123</f>
-        <v>45.9</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>799</v>
+        <v>699</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="5" t="n">
@@ -7433,18 +7517,18 @@
       </c>
       <c r="M124" s="6" t="n">
         <f aca="false">G124*L124</f>
-        <v>79.9</v>
+        <v>69.9</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>4</v>
@@ -7456,7 +7540,7 @@
         <v>297</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>699</v>
+        <v>549</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>298</v>
@@ -7473,39 +7557,39 @@
       </c>
       <c r="M125" s="6" t="n">
         <f aca="false">G125*L125</f>
-        <v>69.9</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>1099</v>
+        <v>1800</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>294</v>
+        <v>354</v>
       </c>
       <c r="K126" s="2"/>
       <c r="L126" s="5" t="n">
@@ -7513,39 +7597,39 @@
       </c>
       <c r="M126" s="6" t="n">
         <f aca="false">G126*L126</f>
-        <v>109.9</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>49</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="5" t="n">
@@ -7558,19 +7642,19 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>139</v>
@@ -7579,13 +7663,13 @@
         <v>135</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="5" t="n">
@@ -7598,34 +7682,34 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>110</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="5" t="n">
@@ -7638,34 +7722,34 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="G130" s="2" t="n">
         <v>33</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="K130" s="2"/>
       <c r="L130" s="5" t="n">
@@ -7678,34 +7762,34 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="G131" s="2" t="n">
         <v>18</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="5" t="n">
@@ -7718,34 +7802,34 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="G132" s="2" t="n">
         <v>21</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J132" s="4" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="K132" s="2"/>
       <c r="L132" s="5" t="n">
@@ -7758,34 +7842,34 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>61</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="K133" s="2"/>
       <c r="L133" s="5" t="n">
@@ -7798,34 +7882,34 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>49</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="K134" s="2"/>
       <c r="L134" s="5" t="n">
@@ -7838,19 +7922,19 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>50</v>
@@ -7859,13 +7943,13 @@
         <v>38</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="5" t="n">
@@ -7878,34 +7962,34 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="G136" s="2" t="n">
         <v>12</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="5" t="n">
@@ -7918,19 +8002,19 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>139</v>
@@ -7939,13 +8023,13 @@
         <v>135</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J137" s="4" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="K137" s="2"/>
       <c r="L137" s="5" t="n">
@@ -7958,19 +8042,19 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>37</v>
@@ -7979,13 +8063,13 @@
         <v>86</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="K138" s="2"/>
       <c r="L138" s="5" t="n">
@@ -7998,34 +8082,34 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="G139" s="2" t="n">
         <v>61</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="5" t="n">
@@ -8038,19 +8122,19 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>50</v>
@@ -8059,13 +8143,13 @@
         <v>38</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="K140" s="2"/>
       <c r="L140" s="5" t="n">
@@ -8078,34 +8162,34 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="G141" s="2" t="n">
         <v>21</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="5" t="n">
@@ -8118,34 +8202,34 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>110</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="5" t="n">
@@ -8158,34 +8242,34 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>121</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="K143" s="2"/>
       <c r="L143" s="5" t="n">
@@ -8198,34 +8282,34 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>88</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="K144" s="2"/>
       <c r="L144" s="5" t="n">
@@ -8238,34 +8322,34 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>61</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="K145" s="2"/>
       <c r="L145" s="5" t="n">
@@ -8278,34 +8362,34 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="G146" s="2" t="n">
         <v>88</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="K146" s="2"/>
       <c r="L146" s="5" t="n">
@@ -8318,34 +8402,34 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="G147" s="2" t="n">
         <v>49</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="5" t="n">
@@ -8358,34 +8442,34 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="G148" s="2" t="n">
         <v>18</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="K148" s="2"/>
       <c r="L148" s="5" t="n">
@@ -8398,34 +8482,34 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="G149" s="2" t="n">
         <v>16</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="K149" s="2"/>
       <c r="L149" s="5" t="n">
@@ -8438,34 +8522,34 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="G150" s="2" t="n">
         <v>12</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="5" t="n">
@@ -8478,34 +8562,34 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="G151" s="2" t="n">
         <v>1002</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="K151" s="2"/>
       <c r="L151" s="5" t="n">
@@ -8518,34 +8602,34 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="G152" s="2" t="n">
         <v>509</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="K152" s="2"/>
       <c r="L152" s="5" t="n">
@@ -8558,34 +8642,34 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G153" s="2" t="n">
         <v>499</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="K153" s="2"/>
       <c r="L153" s="5" t="n">
@@ -8598,34 +8682,34 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="G154" s="2" t="n">
         <v>330</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="K154" s="2"/>
       <c r="L154" s="5" t="n">
@@ -8638,34 +8722,34 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G155" s="2" t="n">
         <v>300</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="K155" s="2"/>
       <c r="L155" s="5" t="n">
@@ -8678,34 +8762,34 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="G156" s="2" t="n">
         <v>330</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="K156" s="2"/>
       <c r="L156" s="5" t="n">
@@ -8718,34 +8802,34 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G157" s="2" t="n">
         <v>300</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="K157" s="2"/>
       <c r="L157" s="5" t="n">
@@ -8758,34 +8842,34 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>409</v>
-      </c>
       <c r="C158" s="2" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="G158" s="2" t="n">
         <v>299</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="K158" s="2"/>
       <c r="L158" s="5" t="n">
@@ -8798,34 +8882,34 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G159" s="2" t="n">
         <v>499</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="K159" s="2"/>
       <c r="L159" s="5" t="n">
@@ -8838,34 +8922,34 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="G160" s="2" t="n">
         <v>1002</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="K160" s="2"/>
       <c r="L160" s="5" t="n">
@@ -8878,34 +8962,34 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="G161" s="2" t="n">
         <v>1002</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="K161" s="2"/>
       <c r="L161" s="5" t="n">
@@ -8918,34 +9002,34 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="G162" s="2" t="n">
         <v>509</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="K162" s="2"/>
       <c r="L162" s="5" t="n">
@@ -8958,34 +9042,34 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G163" s="2" t="n">
         <v>499</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="K163" s="2"/>
       <c r="L163" s="5" t="n">
@@ -8998,34 +9082,34 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G164" s="2" t="n">
         <v>300</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="K164" s="2"/>
       <c r="L164" s="5" t="n">
@@ -9038,34 +9122,34 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="G165" s="2" t="n">
         <v>330</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="K165" s="2"/>
       <c r="L165" s="5" t="n">
@@ -9078,34 +9162,34 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="G166" s="2" t="n">
         <v>330</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="K166" s="2"/>
       <c r="L166" s="5" t="n">
@@ -9118,34 +9202,34 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G167" s="2" t="n">
         <v>300</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="I167" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="K167" s="2"/>
       <c r="L167" s="5" t="n">
@@ -9158,34 +9242,34 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="G168" s="2" t="n">
         <v>299</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="K168" s="2"/>
       <c r="L168" s="5" t="n">
@@ -9198,34 +9282,34 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G169" s="2" t="n">
         <v>499</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="I169" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="K169" s="2"/>
       <c r="L169" s="5" t="n">
@@ -9238,34 +9322,34 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="G170" s="2" t="n">
         <v>1002</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="I170" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="K170" s="2"/>
       <c r="L170" s="5" t="n">
@@ -9278,34 +9362,34 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="G171" s="2" t="n">
         <v>509</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="I171" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="K171" s="2"/>
       <c r="L171" s="5" t="n">
@@ -9318,34 +9402,34 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G172" s="2" t="n">
         <v>499</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="I172" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="K172" s="2"/>
       <c r="L172" s="5" t="n">
@@ -9358,34 +9442,34 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="G173" s="2" t="n">
         <v>1002</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="I173" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="K173" s="2"/>
       <c r="L173" s="5" t="n">
@@ -9398,34 +9482,34 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G174" s="2" t="n">
         <v>300</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="K174" s="2"/>
       <c r="L174" s="5" t="n">
@@ -9438,34 +9522,34 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="G175" s="2" t="n">
         <v>330</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="I175" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="K175" s="2"/>
       <c r="L175" s="5" t="n">
@@ -9478,34 +9562,34 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="G176" s="2" t="n">
         <v>160</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>467</v>
+        <v>495</v>
       </c>
       <c r="I176" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>468</v>
+        <v>496</v>
       </c>
       <c r="K176" s="2"/>
       <c r="L176" s="5" t="n">
@@ -9518,34 +9602,34 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G177" s="2" t="n">
         <v>123</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="I177" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="K177" s="2"/>
       <c r="L177" s="5" t="n">
@@ -9558,34 +9642,34 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
-        <v>473</v>
+        <v>501</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>474</v>
+        <v>502</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>150</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="I178" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="K178" s="2"/>
       <c r="L178" s="5" t="n">
@@ -9598,34 +9682,34 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
-        <v>477</v>
+        <v>505</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G179" s="2" t="n">
         <v>80</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>479</v>
+        <v>507</v>
       </c>
       <c r="I179" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>480</v>
+        <v>508</v>
       </c>
       <c r="K179" s="2"/>
       <c r="L179" s="5" t="n">
@@ -9638,34 +9722,34 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>483</v>
+        <v>511</v>
       </c>
       <c r="G180" s="2" t="n">
         <v>65</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>484</v>
+        <v>512</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="K180" s="2"/>
       <c r="L180" s="5" t="n">
@@ -9678,34 +9762,34 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>474</v>
+        <v>502</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="G181" s="2" t="n">
         <v>150</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="I181" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="K181" s="2"/>
       <c r="L181" s="5" t="n">
@@ -9718,34 +9802,34 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
-        <v>488</v>
+        <v>516</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G182" s="2" t="n">
         <v>123</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="K182" s="2"/>
       <c r="L182" s="5" t="n">
@@ -9758,34 +9842,34 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
-        <v>489</v>
+        <v>517</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G183" s="2" t="n">
         <v>80</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>479</v>
+        <v>507</v>
       </c>
       <c r="I183" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>480</v>
+        <v>508</v>
       </c>
       <c r="K183" s="2"/>
       <c r="L183" s="5" t="n">
@@ -9798,34 +9882,34 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>491</v>
+        <v>519</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>492</v>
+        <v>520</v>
       </c>
       <c r="G184" s="2" t="n">
         <v>95</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>493</v>
+        <v>521</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>494</v>
+        <v>522</v>
       </c>
       <c r="K184" s="2"/>
       <c r="L184" s="5" t="n">
@@ -9838,34 +9922,34 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>483</v>
+        <v>511</v>
       </c>
       <c r="G185" s="2" t="n">
         <v>65</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>484</v>
+        <v>512</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="K185" s="2"/>
       <c r="L185" s="5" t="n">
@@ -9878,34 +9962,34 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>499</v>
+        <v>527</v>
       </c>
       <c r="G186" s="2" t="n">
         <v>91</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="K186" s="2"/>
       <c r="L186" s="5" t="n">
@@ -9918,34 +10002,34 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
-        <v>502</v>
+        <v>530</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>503</v>
+        <v>531</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>504</v>
+        <v>532</v>
       </c>
       <c r="G187" s="2" t="n">
         <v>200</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>505</v>
+        <v>533</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="K187" s="2"/>
       <c r="L187" s="5" t="n">
@@ -9958,34 +10042,34 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>508</v>
+        <v>536</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>499</v>
+        <v>527</v>
       </c>
       <c r="G188" s="2" t="n">
         <v>168</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="I188" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="K188" s="2"/>
       <c r="L188" s="5" t="n">
@@ -9998,34 +10082,34 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="G189" s="2" t="n">
         <v>130</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="I189" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="K189" s="2"/>
       <c r="L189" s="5" t="n">
@@ -10038,34 +10122,34 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
       <c r="G190" s="2" t="n">
         <v>78</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="I190" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="K190" s="2"/>
       <c r="L190" s="5" t="n">
@@ -10078,34 +10162,34 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="G191" s="2" t="n">
         <v>130</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="I191" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="K191" s="2"/>
       <c r="L191" s="5" t="n">
@@ -10118,34 +10202,34 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
       <c r="G192" s="2" t="n">
         <v>78</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="I192" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="K192" s="2"/>
       <c r="L192" s="5" t="n">
@@ -10158,34 +10242,34 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
-        <v>524</v>
+        <v>552</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="G193" s="2" t="n">
         <v>80</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>479</v>
+        <v>507</v>
       </c>
       <c r="I193" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>480</v>
+        <v>508</v>
       </c>
       <c r="K193" s="2"/>
       <c r="L193" s="5" t="n">
@@ -10198,34 +10282,34 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="G194" s="2" t="n">
         <v>43</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="I194" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="K194" s="2"/>
       <c r="L194" s="5" t="n">
@@ -10238,34 +10322,34 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>532</v>
+        <v>560</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>533</v>
+        <v>561</v>
       </c>
       <c r="G195" s="2" t="n">
         <v>124</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="K195" s="2"/>
       <c r="L195" s="5" t="n">
@@ -10278,34 +10362,34 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>538</v>
+        <v>566</v>
       </c>
       <c r="G196" s="2" t="n">
         <v>100</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>540</v>
+        <v>568</v>
       </c>
       <c r="K196" s="2"/>
       <c r="L196" s="5" t="n">
@@ -10318,34 +10402,34 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="G197" s="2" t="n">
         <v>114</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="I197" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>545</v>
+        <v>573</v>
       </c>
       <c r="K197" s="2"/>
       <c r="L197" s="5" t="n">
@@ -10358,34 +10442,34 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="G198" s="2" t="n">
         <v>43</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="I198" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="K198" s="2"/>
       <c r="L198" s="5" t="n">
@@ -10398,34 +10482,34 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>549</v>
+        <v>577</v>
       </c>
       <c r="G199" s="2" t="n">
         <v>18</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="I199" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="K199" s="2"/>
       <c r="L199" s="5" t="n">
@@ -10438,34 +10522,34 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
-        <v>552</v>
+        <v>580</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G200" s="2" t="n">
         <v>1499</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="I200" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="K200" s="2"/>
       <c r="L200" s="5" t="n">
@@ -10478,19 +10562,19 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>180</v>
@@ -10499,13 +10583,13 @@
         <v>359</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="I201" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="K201" s="2"/>
       <c r="L201" s="5" t="n">
@@ -10518,34 +10602,34 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="G202" s="2" t="n">
         <v>799</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="K202" s="2"/>
       <c r="L202" s="5" t="n">
@@ -10558,34 +10642,34 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="D203" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="G203" s="2" t="n">
         <v>1618</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="I203" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="K203" s="2"/>
       <c r="L203" s="5" t="n">
@@ -10598,34 +10682,34 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="D204" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="G204" s="2" t="n">
         <v>563</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="I204" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="K204" s="2"/>
       <c r="L204" s="5" t="n">
@@ -10638,19 +10722,19 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="D205" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>180</v>
@@ -10659,13 +10743,13 @@
         <v>359</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="I205" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="K205" s="2"/>
       <c r="L205" s="5" t="n">
@@ -10678,19 +10762,19 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="D206" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>180</v>
@@ -10699,13 +10783,13 @@
         <v>519</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="I206" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="K206" s="2"/>
       <c r="L206" s="5" t="n">
@@ -10718,34 +10802,34 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="D207" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="G207" s="2" t="n">
         <v>799</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="I207" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="K207" s="2"/>
       <c r="L207" s="5" t="n">
@@ -10758,34 +10842,34 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="D208" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="G208" s="2" t="n">
         <v>563</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="I208" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="K208" s="2"/>
       <c r="L208" s="5" t="n">
@@ -10798,34 +10882,34 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="D209" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G209" s="2" t="n">
         <v>1499</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="I209" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="K209" s="2"/>
       <c r="L209" s="5" t="n">
@@ -10838,34 +10922,34 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="D210" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="G210" s="2" t="n">
         <v>1618</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="I210" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="K210" s="2"/>
       <c r="L210" s="5" t="n">
@@ -10878,34 +10962,34 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="D211" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G211" s="2" t="n">
         <v>1499</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="I211" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="K211" s="2"/>
       <c r="L211" s="5" t="n">
@@ -10918,34 +11002,34 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="D212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="G212" s="2" t="n">
         <v>799</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="I212" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="K212" s="2"/>
       <c r="L212" s="5" t="n">
@@ -10958,19 +11042,19 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="D213" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>180</v>
@@ -10979,13 +11063,13 @@
         <v>519</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="I213" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="K213" s="2"/>
       <c r="L213" s="5" t="n">
@@ -10998,34 +11082,34 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="s">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="D214" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="G214" s="2" t="n">
         <v>563</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="I214" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="K214" s="2"/>
       <c r="L214" s="5" t="n">
@@ -11038,34 +11122,34 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="D215" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G215" s="2" t="n">
         <v>1499</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="I215" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="K215" s="2"/>
       <c r="L215" s="5" t="n">
@@ -11078,19 +11162,19 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="D216" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>180</v>
@@ -11099,13 +11183,13 @@
         <v>359</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="I216" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="K216" s="2"/>
       <c r="L216" s="5" t="n">
@@ -11118,34 +11202,34 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="D217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="G217" s="2" t="n">
         <v>799</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="I217" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="K217" s="2"/>
       <c r="L217" s="5" t="n">
@@ -11158,34 +11242,34 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="D218" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="G218" s="2" t="n">
         <v>1618</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="I218" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="K218" s="2"/>
       <c r="L218" s="5" t="n">
@@ -11198,34 +11282,34 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="D219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="G219" s="2" t="n">
         <v>563</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="I219" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="K219" s="2"/>
       <c r="L219" s="5" t="n">
@@ -11238,19 +11322,19 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="D220" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>180</v>
@@ -11259,13 +11343,13 @@
         <v>359</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="I220" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="K220" s="2"/>
       <c r="L220" s="5" t="n">
@@ -11278,19 +11362,19 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>600</v>
+        <v>628</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="D221" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>180</v>
@@ -11299,13 +11383,13 @@
         <v>519</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="I221" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="K221" s="2"/>
       <c r="L221" s="5" t="n">
@@ -11318,34 +11402,34 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="D222" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="G222" s="2" t="n">
         <v>563</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="I222" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="K222" s="2"/>
       <c r="L222" s="5" t="n">
@@ -11358,34 +11442,34 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
-        <v>602</v>
+        <v>630</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="D223" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="G223" s="2" t="n">
         <v>799</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="I223" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="K223" s="2"/>
       <c r="L223" s="5" t="n">
@@ -11398,34 +11482,34 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
-        <v>603</v>
+        <v>631</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="D224" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G224" s="2" t="n">
         <v>1499</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="I224" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="K224" s="2"/>
       <c r="L224" s="5" t="n">
@@ -11438,34 +11522,34 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>604</v>
+        <v>632</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>606</v>
+        <v>634</v>
       </c>
       <c r="D225" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G225" s="2" t="n">
         <v>549</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="I225" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="K225" s="2"/>
       <c r="L225" s="5" t="n">
@@ -11478,34 +11562,34 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>606</v>
+        <v>634</v>
       </c>
       <c r="D226" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G226" s="2" t="n">
         <v>499</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="I226" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>613</v>
+        <v>641</v>
       </c>
       <c r="K226" s="2"/>
       <c r="L226" s="5" t="n">
@@ -11518,34 +11602,34 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>614</v>
+        <v>642</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>606</v>
+        <v>634</v>
       </c>
       <c r="D227" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="G227" s="2" t="n">
         <v>156</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="I227" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="K227" s="2"/>
       <c r="L227" s="5" t="n">
@@ -11558,34 +11642,34 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>606</v>
+        <v>634</v>
       </c>
       <c r="D228" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="G228" s="2" t="n">
         <v>141</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="I228" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="K228" s="2"/>
       <c r="L228" s="5" t="n">
@@ -11598,34 +11682,34 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
-        <v>624</v>
+        <v>652</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>606</v>
+        <v>634</v>
       </c>
       <c r="D229" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="G229" s="2" t="n">
         <v>112</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="I229" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="K229" s="2"/>
       <c r="L229" s="5" t="n">
@@ -11638,34 +11722,34 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="D230" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G230" s="2" t="n">
         <v>249</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="I230" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="K230" s="2"/>
       <c r="L230" s="5" t="n">
@@ -11678,34 +11762,34 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="s">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="D231" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="G231" s="2" t="n">
         <v>156</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="I231" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="K231" s="2"/>
       <c r="L231" s="5" t="n">
@@ -11718,34 +11802,34 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2" t="s">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="D232" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="G232" s="2" t="n">
         <v>143</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="I232" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="K232" s="2"/>
       <c r="L232" s="5" t="n">
@@ -11758,34 +11842,34 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="s">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="D233" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="G233" s="2" t="n">
         <v>141</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="I233" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="K233" s="2"/>
       <c r="L233" s="5" t="n">
@@ -11798,34 +11882,34 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2" t="s">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="D234" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>642</v>
+        <v>670</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="G234" s="2" t="n">
         <v>96</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>643</v>
+        <v>671</v>
       </c>
       <c r="I234" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>644</v>
+        <v>672</v>
       </c>
       <c r="K234" s="2"/>
       <c r="L234" s="5" t="n">
@@ -11838,34 +11922,34 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="s">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="D235" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G235" s="2" t="n">
         <v>549</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="I235" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="K235" s="2"/>
       <c r="L235" s="5" t="n">
@@ -11878,34 +11962,34 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="s">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="D236" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G236" s="2" t="n">
         <v>249</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="I236" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="K236" s="2"/>
       <c r="L236" s="5" t="n">
@@ -11918,34 +12002,34 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2" t="s">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="D237" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>141</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="I237" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="K237" s="2"/>
       <c r="L237" s="5" t="n">
@@ -11958,34 +12042,34 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="s">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="D238" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="G238" s="2" t="n">
         <v>156</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="I238" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="K238" s="2"/>
       <c r="L238" s="5" t="n">
@@ -11998,34 +12082,34 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2" t="s">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="D239" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="G239" s="2" t="n">
         <v>112</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="I239" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="K239" s="2"/>
       <c r="L239" s="5" t="n">
@@ -12038,34 +12122,34 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="D240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G240" s="2" t="n">
         <v>499</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="I240" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>613</v>
+        <v>641</v>
       </c>
       <c r="K240" s="2"/>
       <c r="L240" s="5" t="n">
@@ -12078,34 +12162,34 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
-        <v>653</v>
+        <v>681</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="D241" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G241" s="2" t="n">
         <v>549</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="I241" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="K241" s="2"/>
       <c r="L241" s="5" t="n">
@@ -12118,34 +12202,34 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="D242" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>655</v>
+        <v>683</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G242" s="2" t="n">
         <v>399</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>656</v>
+        <v>684</v>
       </c>
       <c r="I242" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>657</v>
+        <v>685</v>
       </c>
       <c r="K242" s="2"/>
       <c r="L242" s="5" t="n">
@@ -12158,34 +12242,34 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="s">
-        <v>658</v>
+        <v>686</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="D243" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="G243" s="2" t="n">
         <v>141</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="I243" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="K243" s="2"/>
       <c r="L243" s="5" t="n">
@@ -12198,34 +12282,34 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2" t="s">
-        <v>659</v>
+        <v>687</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="D244" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="G244" s="2" t="n">
         <v>143</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="I244" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="K244" s="2"/>
       <c r="L244" s="5" t="n">
@@ -12238,34 +12322,34 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2" t="s">
-        <v>660</v>
+        <v>688</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="D245" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G245" s="2" t="n">
         <v>549</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="I245" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J245" s="4" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="K245" s="2"/>
       <c r="L245" s="5" t="n">
@@ -12278,34 +12362,34 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2" t="s">
-        <v>662</v>
+        <v>690</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="D246" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G246" s="2" t="n">
         <v>499</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="I246" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>613</v>
+        <v>641</v>
       </c>
       <c r="K246" s="2"/>
       <c r="L246" s="5" t="n">
@@ -12318,34 +12402,34 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2" t="s">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="D247" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>655</v>
+        <v>683</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G247" s="2" t="n">
         <v>399</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>656</v>
+        <v>684</v>
       </c>
       <c r="I247" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>657</v>
+        <v>685</v>
       </c>
       <c r="K247" s="2"/>
       <c r="L247" s="5" t="n">
@@ -12358,34 +12442,34 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="D248" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="G248" s="2" t="n">
         <v>249</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="I248" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="K248" s="2"/>
       <c r="L248" s="5" t="n">
@@ -12398,34 +12482,34 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2" t="s">
-        <v>665</v>
+        <v>693</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="D249" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="G249" s="2" t="n">
         <v>156</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="I249" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="K249" s="2"/>
       <c r="L249" s="5" t="n">
